--- a/docs/oc-regiones/suministro-de-combustibles/los-rios.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M302"/>
+  <dimension ref="A1:M305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>10687.21</v>
+        <v>10596.7</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3206.16</v>
+        <v>3179.01</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>24640.44</v>
+        <v>24513.84</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3380.84</v>
+        <v>3345.44</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>11061.27</v>
+        <v>10945.43</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2351.19</v>
+        <v>2326.57</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2885.55</v>
+        <v>2855.33</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4274.89</v>
+        <v>4251.52</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3740.53</v>
+        <v>3720.04</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5984.84</v>
+        <v>5952.06</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>11755.94</v>
+        <v>11740.97</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>26987.2</v>
+        <v>26952.85</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>21374.43</v>
+        <v>21347.22</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2244.32</v>
+        <v>2252.32</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>12290.3</v>
+        <v>12334.16</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3206.16</v>
+        <v>3217.61</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3206.16</v>
+        <v>3217.61</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>33664.66</v>
+        <v>33775.38</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2990.63</v>
+        <v>3000.47</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4274.89</v>
+        <v>4288.95</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>5343.61</v>
+        <v>5435.85</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>11221.58</v>
+        <v>11415.28</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>10687.21</v>
+        <v>10736.99</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7481.05</v>
+        <v>7534.98</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2671.8</v>
+        <v>2691.07</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>37084.63</v>
+        <v>37351.99</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>6052.25</v>
+        <v>6041.51</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>5237.21</v>
+        <v>5215.62</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5343.61</v>
+        <v>5335.33</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>8549.77</v>
+        <v>8593.93</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8549.77</v>
+        <v>8610.110000000001</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>32231.16</v>
+        <v>31814.56</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2433.32</v>
+        <v>2402.41</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>6549.05</v>
+        <v>6483.89</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2837.92</v>
+        <v>2827.75</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>10915.09</v>
+        <v>10875.95</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2292.17</v>
+        <v>2287.21</v>
       </c>
     </row>
     <row r="39">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2396.49</v>
+        <v>2391.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5751-5717-CM25</t>
+          <t>3853-837-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2852,17 +2852,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2292.17</v>
+        <v>16337.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3853-837-CM25</t>
+          <t>1723-797-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>16372.63</v>
+        <v>11436.04</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1723-797-CM25</t>
+          <t>5751-5717-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2974,17 +2974,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>11460.84</v>
+        <v>2287.21</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2277.43</v>
+        <v>2267.89</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>11460.84</v>
+        <v>11412.8</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2401.32</v>
+        <v>2391.25</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>25499.34</v>
+        <v>25204.23</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>16809.24</v>
+        <v>16614.7</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>10369.33</v>
+        <v>10281.5</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3110.8</v>
+        <v>3122.74</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2336.19</v>
+        <v>2342.39</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>5457.54</v>
+        <v>5449.89</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>5216.75</v>
+        <v>5223.44</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5457.54</v>
+        <v>5464.54</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2279.7</v>
+        <v>2282.62</v>
       </c>
     </row>
     <row r="55">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>3820.28</v>
+        <v>3846.58</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1057545-6469-CM25</t>
+          <t>2906-293-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>11834.14</v>
+        <v>13210.04</v>
       </c>
     </row>
     <row r="57">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>5457.54</v>
+        <v>5504.18</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2906-293-CM25</t>
+          <t>1057545-6468-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>13098.11</v>
+        <v>3972.37</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1057545-6468-CM25</t>
+          <t>3335-2344-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4011,17 +4011,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3938.71</v>
+        <v>5523</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3335-2344-CM25</t>
+          <t>2909-1207-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4072,17 +4072,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>5476.21</v>
+        <v>2531.92</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2909-1207-CM25</t>
+          <t>1057545-6469-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2510.47</v>
+        <v>11935.27</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>21830.18</v>
+        <v>22064.34</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2728.77</v>
+        <v>2762.31</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4366.04</v>
+        <v>4419.69</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>10915.09</v>
+        <v>11049.24</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>5457.54</v>
+        <v>5527.67</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>13401.98</v>
+        <v>13574.19</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2292.17</v>
+        <v>2321.62</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>9714.43</v>
+        <v>9839.26</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>4618.79</v>
+        <v>4678.14</v>
       </c>
     </row>
     <row r="71">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>54575.44</v>
+        <v>54873.9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>909103-139-CM25</t>
+          <t>5472-165-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4804,17 +4804,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.978.950-4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2292.17</v>
+        <v>3120.86</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5472-164-CM25</t>
+          <t>5612-229-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.978.950-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>6549.05</v>
+        <v>3554.53</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5472-165-CM25</t>
+          <t>909103-139-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4926,17 +4926,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.978.950-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>3103.88</v>
+        <v>2304.7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5612-229-CM25</t>
+          <t>5472-164-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.978.950-4</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS RÍOS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>3535.19</v>
+        <v>6584.87</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3493.45</v>
+        <v>3512.55</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2859.75</v>
+        <v>2875.39</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>13575.19</v>
+        <v>13228.53</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2623.46</v>
+        <v>2556.47</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>5656.33</v>
+        <v>5546</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>25286.05</v>
+        <v>24792.86</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>4164.13</v>
+        <v>4082.91</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2375.66</v>
+        <v>2320.08</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>13575.19</v>
+        <v>13548.45</v>
       </c>
     </row>
     <row r="85">
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>3393.8</v>
+        <v>3393.82</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1267885-46-CM26</t>
+          <t>4777-15-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5658,17 +5658,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>71.016.300-6</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>10294.52</v>
+        <v>27602.72</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3568-23-CM26</t>
+          <t>3762-25-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.201.200-3</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>22625.31</v>
+        <v>12435.42</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3762-25-CM26</t>
+          <t>1267885-46-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5780,17 +5780,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>71.016.300-6</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>12443.92</v>
+        <v>10287.48</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4777-15-CM26</t>
+          <t>3568-23-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.201.200-3</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>27621.59</v>
+        <v>22609.86</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>593649-1-CM26</t>
+          <t>1057552-16-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>61.607.508-K</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>5178.5</v>
+        <v>5636.92</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1057547-752-CM26</t>
+          <t>593649-1-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2988.68</v>
+        <v>5160.72</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5625-6-CM26</t>
+          <t>1057547-752-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.978.990-3</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3620.05</v>
+        <v>2978.42</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3335-19-CM26</t>
+          <t>5625-6-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6085,17 +6085,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.978.990-3</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>3129.12</v>
+        <v>3607.63</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1057552-16-CM26</t>
+          <t>3335-19-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6146,17 +6146,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.607.508-K</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>5656.33</v>
+        <v>3118.38</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>22625.31</v>
+        <v>22505.8</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>4638.19</v>
+        <v>4609.12</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3167.54</v>
+        <v>3188.3</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3959.43</v>
+        <v>4012.75</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2375.66</v>
+        <v>2407.65</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2375.66</v>
+        <v>2407.65</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2375.66</v>
+        <v>2407.65</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>13575.19</v>
+        <v>13758</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>4525.06</v>
+        <v>4593.95</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>45250.62</v>
+        <v>46351.02</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2367.21</v>
+        <v>2424.77</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2375.66</v>
+        <v>2433.43</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>5564.43</v>
+        <v>5705.1</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2828.16</v>
+        <v>2899.66</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>7918.8</v>
+        <v>8118.98</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>12813.85</v>
+        <v>13194.71</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>15837.72</v>
+        <v>16308.46</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>27758.06</v>
+        <v>27659.23</v>
       </c>
     </row>
     <row r="113">
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>9280.530000000001</v>
+        <v>9328.469999999999</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3568-112-CM26</t>
+          <t>3850-8-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7366,17 +7366,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.201.200-3</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>34801.98</v>
+        <v>2448.72</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1057548-88-CM26</t>
+          <t>3568-112-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.607.503-9</t>
+          <t>69.201.200-3</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>8120.46</v>
+        <v>34981.75</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3850-8-CM26</t>
+          <t>1057548-88-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7488,17 +7488,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>61.607.503-9</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>2436.14</v>
+        <v>8162.41</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>4060.23</v>
+        <v>4071.38</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>3480.2</v>
+        <v>3489.75</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>3480.2</v>
+        <v>3511.85</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>5800.33</v>
+        <v>5853.09</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>2436.14</v>
+        <v>2453.1</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>3132.18</v>
+        <v>3160.08</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>3480.2</v>
+        <v>3511.19</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>29269.24</v>
+        <v>29219.08</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2922.63</v>
+        <v>2919.62</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2579.78</v>
+        <v>2577.12</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>6960.4</v>
+        <v>6953.22</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>17203.76</v>
+        <v>17080.51</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>19721.12</v>
+        <v>19692.11</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>11600.66</v>
+        <v>11532.3</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>2679.75</v>
+        <v>2663.47</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>13920.79</v>
+        <v>13867.06</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>5605.12</v>
+        <v>5634.14</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>10672.61</v>
+        <v>10682.89</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3297.09</v>
+        <v>3442.7</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2307.96</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>23791.8</v>
+        <v>24482.87</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>32970.9</v>
+        <v>33100.89</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2747.58</v>
+        <v>2754.34</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>5495.15</v>
+        <v>5424.41</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2747.58</v>
+        <v>2712.2</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2307.96</v>
+        <v>2297.64</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>2951.07</v>
+        <v>2953.61</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>16485.45</v>
+        <v>16499.65</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>9891.27</v>
+        <v>9899.790000000001</v>
       </c>
     </row>
     <row r="146">
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>10990.3</v>
+        <v>11035.7</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>926853-4-CM26</t>
+          <t>2986-88-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9379,17 +9379,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>3472.94</v>
+        <v>10959.99</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1057545-268-CM26</t>
+          <t>926853-4-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>Zona de Bienestar Valdivia</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>8721.9</v>
+        <v>3463.36</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2986-88-CM26</t>
+          <t>1057545-268-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9501,17 +9501,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>10990.3</v>
+        <v>8697.84</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2307.96</v>
+        <v>2281.32</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>4945.64</v>
+        <v>4871.87</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>27898.48</v>
+        <v>27482.37</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2747.58</v>
+        <v>2706.59</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>8792.24</v>
+        <v>8661.1</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>3846.61</v>
+        <v>3824.51</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>5495.15</v>
+        <v>5463.59</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2307.96</v>
+        <v>2294.71</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3297.09</v>
+        <v>3278.15</v>
       </c>
     </row>
     <row r="159">
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>10770.49</v>
+        <v>10708.63</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3762-241-CM26</t>
+          <t>2027-16-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10172,17 +10172,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>60.902.015-6</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>Depto. Provincial Educación Valdivia</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3297.09</v>
+        <v>2839.17</v>
       </c>
     </row>
     <row r="161">
@@ -10268,13 +10268,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>3297.09</v>
+        <v>3275.97</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2027-16-CM26</t>
+          <t>3762-241-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10294,17 +10294,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>60.902.015-6</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Depto. Provincial Educación Valdivia</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2857.48</v>
+        <v>3275.97</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>16485.45</v>
+        <v>16414.43</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2411.27</v>
+        <v>2400.88</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>14751.19</v>
+        <v>14433.82</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>43961.2</v>
+        <v>42938.27</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>38371.54</v>
+        <v>37478.67</v>
       </c>
     </row>
     <row r="168">
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>6044.67</v>
+        <v>5904.01</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>509876-21-CM26</t>
+          <t>5740-101-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10741,12 +10741,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>2335.49</v>
+        <v>12938.56</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>5740-101-CM26</t>
+          <t>509876-21-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>Servicio Nacional del Patrimonio Cultural</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>13364.72</v>
+        <v>2261.01</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2784.32</v>
+        <v>2695.53</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>22274.54</v>
+        <v>21564.27</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>4205.14</v>
+        <v>4122.21</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>13364.72</v>
+        <v>13101.15</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>22831.4</v>
+        <v>22381.13</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>2784.32</v>
+        <v>2729.41</v>
       </c>
     </row>
     <row r="177">
@@ -11244,13 +11244,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>2450.2</v>
+        <v>2385.68</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>4053-169-CM26</t>
+          <t>3762-277-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11275,12 +11275,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11305,13 +11305,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>24195.72</v>
+        <v>12028.83</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>3762-277-CM26</t>
+          <t>4053-169-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11336,12 +11336,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>12251</v>
+        <v>23756.93</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1057549-149-CM26</t>
+          <t>3334-119-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11392,17 +11392,17 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.607.504-7</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11412,12 +11412,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11427,13 +11427,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>3341.18</v>
+        <v>4591.33</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>3334-119-CM26</t>
+          <t>1057549-149-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11453,17 +11453,17 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.607.504-7</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>4676.13</v>
+        <v>3280.59</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>7796.09</v>
+        <v>7828.49</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2784.32</v>
+        <v>2807.95</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>4454.91</v>
+        <v>4447.46</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>16705.9</v>
+        <v>16911.51</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>29433.13</v>
+        <v>29824.97</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>15592.18</v>
+        <v>15799.75</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>4508.9</v>
+        <v>4568.92</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>5568.63</v>
+        <v>5641.3</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>4654.71</v>
+        <v>4715.45</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>12251</v>
+        <v>12410.87</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>10023.54</v>
+        <v>10154.35</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>16705.9</v>
+        <v>17117.03</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>5244.7</v>
+        <v>5343.9</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>3341.18</v>
+        <v>3404.37</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>27843.17</v>
+        <v>28093.99</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>15035.31</v>
+        <v>15066.46</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>45340.38</v>
+        <v>45434.3</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>10023.54</v>
+        <v>10044.31</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>11137.27</v>
+        <v>11089.43</v>
       </c>
     </row>
     <row r="201">
@@ -12708,13 +12708,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>3341.18</v>
+        <v>3326.83</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1057551-198-CM26</t>
+          <t>696750-15-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12734,17 +12734,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>61.607.507-1</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE P</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12769,13 +12769,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>3898.04</v>
+        <v>7762.6</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>696750-15-CM26</t>
+          <t>1057551-198-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12795,17 +12795,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.607.507-1</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>7796.09</v>
+        <v>3881.3</v>
       </c>
     </row>
     <row r="204">
@@ -12891,13 +12891,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>17935.96</v>
+        <v>17828.47</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1057553-156-CM26</t>
+          <t>1057547-6297-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>61.607.509-8</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12937,12 +12937,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -12952,13 +12952,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>3342.1</v>
+        <v>4202.29</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1057547-6297-CM26</t>
+          <t>1057549-194-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.607.504-7</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -13013,13 +13013,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>4260.21</v>
+        <v>3296.67</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1057549-194-CM26</t>
+          <t>1057553-156-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13044,12 +13044,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>61.607.504-7</t>
+          <t>61.607.509-8</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>3342.1</v>
+        <v>3296.67</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>23135.28</v>
+        <v>22820.74</v>
       </c>
     </row>
     <row r="209">
@@ -13196,13 +13196,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>44561.4</v>
+        <v>44181.32</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>3335-455-CM26</t>
+          <t>909103-31-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13227,12 +13227,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13242,12 +13242,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -13257,13 +13257,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>7176.75</v>
+        <v>2372.23</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>909103-31-CM26</t>
+          <t>3335-455-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13288,12 +13288,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13303,12 +13303,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>2359.53</v>
+        <v>7215.4</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>5570.17</v>
+        <v>5591.28</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>2359.12</v>
+        <v>2353.17</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>3342.1</v>
+        <v>3333.67</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>2361.75</v>
+        <v>2355.79</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>4456.14</v>
+        <v>4498.48</v>
       </c>
     </row>
     <row r="217">
@@ -13684,13 +13684,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>4456.14</v>
+        <v>4498.48</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>5612-68-CM26</t>
+          <t>1067355-228-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13715,12 +13715,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.980.670-0</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13730,12 +13730,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -13745,13 +13745,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>2617.98</v>
+        <v>2805.84</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2905-331-CM26</t>
+          <t>5612-68-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13806,13 +13806,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>13368.42</v>
+        <v>2637.49</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1067355-228-CM26</t>
+          <t>2905-331-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13837,12 +13837,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.980.670-0</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13852,12 +13852,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>2785.09</v>
+        <v>13468.01</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>9141.309999999999</v>
+        <v>9050.139999999999</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>4790.1</v>
+        <v>4742.32</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>47216.26</v>
+        <v>47009.29</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>12254.38</v>
+        <v>12200.67</v>
       </c>
     </row>
     <row r="225">
@@ -14172,13 +14172,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>11363.51</v>
+        <v>11313.7</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1057552-388-CM26</t>
+          <t>5612-74-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14203,12 +14203,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.607.508-K</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14233,13 +14233,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>7798.24</v>
+        <v>39226.06</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>5612-74-CM26</t>
+          <t>1057552-388-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14264,12 +14264,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.607.508-K</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>39657.46</v>
+        <v>7713.41</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>6684.21</v>
+        <v>6669.04</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>2359.12</v>
+        <v>2353.3</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>12254.38</v>
+        <v>12314.58</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>2359.12</v>
+        <v>2366.63</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>3342.1</v>
+        <v>3359.88</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>24352.87</v>
+        <v>24701.34</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>4333.82</v>
+        <v>4395.83</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>36772.83</v>
+        <v>37204.2</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>3874.32</v>
+        <v>3919.77</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>12176.43</v>
+        <v>12382.37</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>11069.49</v>
+        <v>11256.7</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>9962.540000000001</v>
+        <v>10131.03</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>3320.85</v>
+        <v>3377.01</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>10958.79</v>
+        <v>11144.13</v>
       </c>
     </row>
     <row r="242">
@@ -15209,13 +15209,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2545.98</v>
+        <v>2571.87</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1057548-604-CM26</t>
+          <t>1057547-8422-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15240,12 +15240,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.607.503-9</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15255,12 +15255,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -15270,13 +15270,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>5534.74</v>
+        <v>4469.32</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5625-36-CM26</t>
+          <t>1057548-604-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.978.990-3</t>
+          <t>61.607.503-9</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15331,13 +15331,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>3320.85</v>
+        <v>5586.65</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1057547-8422-CM26</t>
+          <t>5625-36-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.978.990-3</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>4427.79</v>
+        <v>3351.99</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>2435.29</v>
+        <v>2416.81</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>4427.79</v>
+        <v>4394.2</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>46491.84</v>
+        <v>46139.14</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>3320.85</v>
+        <v>3295.65</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>16604.23</v>
+        <v>16368.58</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>9392.77</v>
+        <v>9259.459999999999</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>5259.59</v>
+        <v>5184.95</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>15497.28</v>
+        <v>15401.2</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>2374.6</v>
+        <v>2359.88</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>40165.49</v>
+        <v>40347.91</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2767.37</v>
+        <v>2808.58</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>2553.79</v>
+        <v>2602.34</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>12176.43</v>
+        <v>12407.93</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>4322.56</v>
+        <v>4404.74</v>
       </c>
     </row>
     <row r="260">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>3874.32</v>
+        <v>3961.7</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1057549-283-CM26</t>
+          <t>1057552-537-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16338,12 +16338,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.607.504-7</t>
+          <t>61.607.508-K</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16368,13 +16368,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>3320.85</v>
+        <v>7772.6</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1057552-537-CM26</t>
+          <t>1057549-283-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16399,12 +16399,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.607.508-K</t>
+          <t>61.607.504-7</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>7748.64</v>
+        <v>3331.11</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>23245.92</v>
+        <v>23317.79</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>22138.97</v>
+        <v>21844.08</v>
       </c>
     </row>
     <row r="265">
@@ -16612,13 +16612,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>3320.85</v>
+        <v>3276.61</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1057553-230-CM26</t>
+          <t>909103-67-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16643,12 +16643,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>61.607.509-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16673,13 +16673,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>3320.85</v>
+        <v>2453.73</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>909103-67-CM26</t>
+          <t>1057553-230-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -16704,12 +16704,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.607.509-8</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>2490.63</v>
+        <v>3271.64</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>2379.94</v>
+        <v>2331.03</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>9559.92</v>
+        <v>9650.73</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>11815.63</v>
+        <v>11927.87</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>3759.52</v>
+        <v>3795.23</v>
       </c>
     </row>
     <row r="272">
@@ -17039,13 +17039,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>3692.92</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1057548-705-CM26</t>
+          <t>4062-468-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>61.607.503-9</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17100,13 +17100,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>5370.74</v>
+        <v>33046.85</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>4062-468-CM26</t>
+          <t>1057548-705-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17131,12 +17131,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>61.607.503-9</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17161,13 +17161,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>32918.35</v>
+        <v>5391.71</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2905-451-CM26</t>
+          <t>5657-196-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17187,17 +17187,17 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17222,13 +17222,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>15038.08</v>
+        <v>2386.89</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>5418-146-CM26</t>
+          <t>1218393-257-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17253,12 +17253,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>53.335.808-K</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>CONSULTORIO EXTERNO VALDIVIA</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17268,12 +17268,12 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K276" t="inlineStr"/>
@@ -17283,13 +17283,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>5370.74</v>
+        <v>6509.71</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1218393-257-CM26</t>
+          <t>5418-146-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17314,12 +17314,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>53.335.808-K</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>CONSULTORIO EXTERNO VALDIVIA</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17329,12 +17329,12 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K277" t="inlineStr"/>
@@ -17344,13 +17344,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>6444.89</v>
+        <v>5424.76</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>5657-196-CM26</t>
+          <t>2905-451-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17370,17 +17370,17 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>2363.13</v>
+        <v>15189.32</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>42965.94</v>
+        <v>43184.89</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>3759.52</v>
+        <v>3774.15</v>
       </c>
     </row>
     <row r="281">
@@ -17588,13 +17588,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>9640.48</v>
+        <v>9662.59</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2909-405-CM26</t>
+          <t>3789-424-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17619,12 +17619,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17634,12 +17634,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K282" t="inlineStr"/>
@@ -17649,13 +17649,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2309.42</v>
+        <v>4866.02</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>3789-424-CM26</t>
+          <t>2909-405-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17680,12 +17680,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17695,12 +17695,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K283" t="inlineStr"/>
@@ -17710,13 +17710,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>4833.67</v>
+        <v>2324.88</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>4777-561-CM26</t>
+          <t>3762-582-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17741,12 +17741,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17756,12 +17756,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K284" t="inlineStr"/>
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>39749.33</v>
+        <v>11898.32</v>
       </c>
     </row>
     <row r="285">
@@ -17832,13 +17832,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>4522.73</v>
+        <v>4554.38</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>3762-582-CM26</t>
+          <t>4777-561-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -17863,12 +17863,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -17878,12 +17878,12 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K286" t="inlineStr"/>
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>11815.63</v>
+        <v>40027.51</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>2534.11</v>
+        <v>2526.1</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>10741.48</v>
+        <v>10718.11</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>18455.48</v>
+        <v>18415.33</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>4833.67</v>
+        <v>4823.15</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>2309.42</v>
+        <v>2304.79</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>9667.34</v>
+        <v>9647.959999999999</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>3222.45</v>
+        <v>3203.79</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>3222.45</v>
+        <v>3170.44</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>2685.37</v>
+        <v>2642.32</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>15038.08</v>
+        <v>14863.1</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>3222.45</v>
+        <v>3184.95</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>2685.37</v>
+        <v>2670.48</v>
       </c>
     </row>
     <row r="299">
@@ -18686,13 +18686,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>5370.74</v>
+        <v>5340.97</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>3762-626-CM26</t>
+          <t>2906-105-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -18712,17 +18712,17 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>11815.63</v>
+        <v>22446.21</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2906-105-CM26</t>
+          <t>3762-626-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -18773,17 +18773,17 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>22557.12</v>
+        <v>11757.54</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,190 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>5370.74</v>
+        <v>5406.69</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>620039-14-CM26</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>61.533.000-0</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M303" s="2" t="n">
+        <v>5471.3</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>1495209-18-CM26</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M304" s="2" t="n">
+        <v>24489.71</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>3568-552-CM26</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>69.201.200-3</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M305" s="2" t="n">
+        <v>43378.3</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/suministro-de-combustibles/los-rios.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/los-rios.xlsx
@@ -562,7 +562,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9727,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9792,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9922,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +10052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10442,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10507,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10572,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10832,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10897,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10962,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +11027,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +11092,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11287,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11677,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11742,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11872,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +12002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +12067,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +12132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12392,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12457,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12782,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12912,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12977,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +13042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +13107,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +13172,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13237,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13627,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13692,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +14017,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +14082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +14147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14212,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14537,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14602,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14667,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14732,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14862,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14927,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14992,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +15057,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +15122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +15187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15447,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15512,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15577,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15772,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15902,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15967,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +16032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +16097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +16162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +16227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16292,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16357,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16682,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +17007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +17072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +17137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +17202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17397,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17592,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17657,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17722,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17852,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +18047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +18112,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +18177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +18242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18437,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18567,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +19022,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +19087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +19152,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +19217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +19282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19347,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19412,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19542,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +20062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +20127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +20192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +20257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +20322,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +20387,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20452,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20582,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20777,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20842,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +21037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +21102,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +21167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +21232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +21297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +21362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21427,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +21557,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +22012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +22077,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +22142,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +22207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +22272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +22337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +22402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22467,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22597,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22727,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +23052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +23117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +23182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +23247,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +23312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +23377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +23442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +23507,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +23572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23637,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +23702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23767,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23897,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23962,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +24027,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +24092,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +24157,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +24222,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +24287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +24352,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +24417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +24482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +24547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +24612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +24677,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23254,7 +24742,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24872,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +24937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +25002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +25067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +25132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +25197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23742,7 +25262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +25327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +25392,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23925,7 +25457,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +25522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +25587,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +25652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +25717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25782,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +25847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25912,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25977,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +26042,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +26107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +26172,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +26237,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +26302,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +26367,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +26432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +26497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +26562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +26627,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +26692,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +26757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +26822,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +27017,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +27082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +27147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25572,7 +27212,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +27277,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +27342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25755,7 +27407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +27472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25877,7 +27537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +27602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +27667,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +27732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +27927,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +27992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26365,7 +28057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +28122,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +28187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +28252,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +28317,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +28382,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +28447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26792,7 +28512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +28577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +28642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +28707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28837,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +28902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +29032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +29097,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +29162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +29227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27524,7 +29292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27585,7 +29357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +29422,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +29487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +29552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +29617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +29682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +29747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +29877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +29942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +30007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +30072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +30137,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +30202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +30267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +30332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +30397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28622,7 +30462,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +30527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +30592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28805,7 +30657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28866,7 +30722,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28927,7 +30787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28988,7 +30852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30917,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29110,7 +30982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29171,7 +31047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29232,7 +31112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +31177,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29354,7 +31242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +31307,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29476,7 +31372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29537,7 +31437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29598,7 +31502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +31567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29720,7 +31632,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29781,7 +31697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29842,7 +31762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29903,7 +31827,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29964,7 +31892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30025,7 +31957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30086,7 +32022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30147,7 +32087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30208,7 +32152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30269,7 +32217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +32282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +32347,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30452,7 +32412,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30513,7 +32477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30574,7 +32542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30635,7 +32607,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30696,7 +32672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +32737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30818,7 +32802,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +32867,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30940,7 +32932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31001,7 +32997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31062,7 +33062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +33127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31184,7 +33192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31245,7 +33257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31306,7 +33322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31367,7 +33387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31428,7 +33452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31489,7 +33517,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31550,7 +33582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31611,7 +33647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31672,7 +33712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31733,7 +33777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31794,7 +33842,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31855,7 +33907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31916,7 +33972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31977,7 +34037,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32038,7 +34102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32099,7 +34167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +34232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32221,7 +34297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32282,7 +34362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32343,7 +34427,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32404,7 +34492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32465,7 +34557,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32526,7 +34622,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32587,7 +34687,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32648,7 +34752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32709,7 +34817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32770,7 +34882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32831,7 +34947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32892,7 +35012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32953,7 +35077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33014,7 +35142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33075,7 +35207,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33136,7 +35272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33197,7 +35337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33258,7 +35402,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33319,7 +35467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33380,7 +35532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33441,7 +35597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33502,7 +35662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33563,7 +35727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33624,7 +35792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33685,7 +35857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33746,7 +35922,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33807,7 +35987,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33868,7 +36052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33929,7 +36117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33990,7 +36182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34051,7 +36247,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34112,7 +36312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34173,7 +36377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34234,7 +36442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34295,7 +36507,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34356,7 +36572,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34417,7 +36637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34478,7 +36702,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34539,7 +36767,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34600,7 +36832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34661,7 +36897,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34722,7 +36962,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34783,7 +37027,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34844,7 +37092,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34905,7 +37157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34966,7 +37222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35027,7 +37287,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35088,7 +37352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35149,7 +37417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35210,7 +37482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35271,7 +37547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35332,7 +37612,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35393,7 +37677,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35454,7 +37742,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35515,7 +37807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35576,7 +37872,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35637,7 +37937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35698,7 +38002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35759,7 +38067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35820,7 +38132,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35881,7 +38197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35942,7 +38262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36003,7 +38327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36064,7 +38392,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36125,7 +38457,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36186,7 +38522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36247,7 +38587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36308,7 +38652,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36369,7 +38717,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36430,7 +38782,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36491,7 +38847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36552,7 +38912,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36613,7 +38977,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36674,7 +39042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36735,7 +39107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36796,7 +39172,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36857,7 +39237,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36918,7 +39302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36979,7 +39367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37040,7 +39432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37101,7 +39497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37162,7 +39562,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37223,7 +39627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37284,7 +39692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37345,7 +39757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37406,7 +39822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37467,7 +39887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37528,7 +39952,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37589,7 +40017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37650,7 +40082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37711,7 +40147,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37772,7 +40212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37833,7 +40277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37894,7 +40342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37955,7 +40407,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38016,7 +40472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38077,7 +40537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38138,7 +40602,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38199,7 +40667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38260,7 +40732,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38321,7 +40797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38382,7 +40862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38443,7 +40927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38504,7 +40992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38565,7 +41057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38626,7 +41122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38687,7 +41187,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38748,7 +41252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38809,7 +41317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38870,7 +41382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38931,7 +41447,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38992,7 +41512,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39053,7 +41577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39114,7 +41642,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39175,7 +41707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39236,7 +41772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39297,7 +41837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39358,7 +41902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39419,7 +41967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39480,7 +42032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39541,7 +42097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39602,7 +42162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39663,7 +42227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39724,7 +42292,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39785,7 +42357,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39846,7 +42422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39907,7 +42487,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39968,7 +42552,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40029,7 +42617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40090,7 +42682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40151,7 +42747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40212,7 +42812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40273,7 +42877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40334,7 +42942,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40395,7 +43007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40456,7 +43072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40517,7 +43137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40578,7 +43202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40639,7 +43267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40700,7 +43332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40761,7 +43397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40822,7 +43462,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40883,7 +43527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40944,7 +43592,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41005,7 +43657,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41066,7 +43722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41127,7 +43787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41188,7 +43852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41249,7 +43917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41310,7 +43982,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41371,7 +44047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41432,7 +44112,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41493,7 +44177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
